--- a/research/traditional_assets/database/data/georgia/georgia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/georgia/georgia_investments_asset_management.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>1.124373956594324</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1.124373956594324</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.9682804674457429</v>
+        <v>0.9850687622789783</v>
       </c>
       <c r="J2">
-        <v>0.9682804674457429</v>
+        <v>0.9850687622789783</v>
       </c>
       <c r="K2">
-        <v>336.3</v>
+        <v>-70.5</v>
       </c>
       <c r="L2">
-        <v>2.807178631051753</v>
+        <v>-0.2770137524557957</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -632,26 +632,11 @@
       <c r="V2">
         <v>0</v>
       </c>
-      <c r="W2">
-        <v>0.8579081632653062</v>
-      </c>
       <c r="X2">
-        <v>0.06524340450733665</v>
-      </c>
-      <c r="Y2">
-        <v>0.7926647587579695</v>
-      </c>
-      <c r="Z2">
-        <v>0.305878327831098</v>
-      </c>
-      <c r="AA2">
-        <v>0.2961760102538177</v>
+        <v>0.1020052760592112</v>
       </c>
       <c r="AB2">
-        <v>0.06524340450733665</v>
-      </c>
-      <c r="AC2">
-        <v>0.2309326057464811</v>
+        <v>0.1020052760592112</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -678,16 +663,13 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.55</v>
-      </c>
-      <c r="AO2">
-        <v>32.67605633802817</v>
+        <v>-0.983</v>
       </c>
       <c r="AQ2">
-        <v>32.67605633802817</v>
+        <v>-255.0356052899288</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +689,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>1.124373956594324</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1.124373956594324</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9682804674457429</v>
+        <v>0.9850687622789783</v>
       </c>
       <c r="J3">
-        <v>0.9682804674457429</v>
+        <v>0.9850687622789783</v>
       </c>
       <c r="K3">
-        <v>336.3</v>
+        <v>-70.5</v>
       </c>
       <c r="L3">
-        <v>2.807178631051753</v>
+        <v>-0.2770137524557957</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -731,7 +713,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -740,7 +722,7 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -751,26 +733,11 @@
       <c r="V3">
         <v>0</v>
       </c>
-      <c r="W3">
-        <v>0.8579081632653062</v>
-      </c>
       <c r="X3">
-        <v>0.06524340450733665</v>
-      </c>
-      <c r="Y3">
-        <v>0.7926647587579695</v>
-      </c>
-      <c r="Z3">
-        <v>0.305878327831098</v>
-      </c>
-      <c r="AA3">
-        <v>0.2961760102538177</v>
+        <v>0.1020052760592112</v>
       </c>
       <c r="AB3">
-        <v>0.06524340450733665</v>
-      </c>
-      <c r="AC3">
-        <v>0.2309326057464811</v>
+        <v>0.1020052760592112</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,16 +764,13 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.55</v>
-      </c>
-      <c r="AO3">
-        <v>32.67605633802817</v>
+        <v>-0.983</v>
       </c>
       <c r="AQ3">
-        <v>32.67605633802817</v>
+        <v>-255.0356052899288</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/georgia/georgia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/georgia/georgia_investments_asset_management.xlsx
@@ -587,6 +587,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.376</v>
+      </c>
+      <c r="E2">
+        <v>1.452</v>
+      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -594,16 +600,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.9850687622789783</v>
+        <v>0.9622266401590458</v>
       </c>
       <c r="J2">
-        <v>0.9850687622789783</v>
+        <v>0.9622266401590458</v>
       </c>
       <c r="K2">
-        <v>-70.5</v>
+        <v>273.8</v>
       </c>
       <c r="L2">
-        <v>-0.2770137524557957</v>
+        <v>5.443339960238569</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -632,11 +638,26 @@
       <c r="V2">
         <v>0</v>
       </c>
+      <c r="W2">
+        <v>0.3328066123738909</v>
+      </c>
       <c r="X2">
-        <v>0.1020052760592112</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="Y2">
+        <v>0.2480096839059283</v>
+      </c>
+      <c r="Z2">
+        <v>0.06114014829220858</v>
+      </c>
+      <c r="AA2">
+        <v>0.05883067947003768</v>
       </c>
       <c r="AB2">
-        <v>0.1020052760592112</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="AC2">
+        <v>-0.02596624899792487</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.983</v>
+        <v>-5.77</v>
       </c>
       <c r="AQ2">
-        <v>-255.0356052899288</v>
+        <v>-8.388214904679376</v>
       </c>
     </row>
     <row r="3">
@@ -688,6 +709,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.376</v>
+      </c>
+      <c r="E3">
+        <v>1.452</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -695,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9850687622789783</v>
+        <v>0.9622266401590458</v>
       </c>
       <c r="J3">
-        <v>0.9850687622789783</v>
+        <v>0.9622266401590458</v>
       </c>
       <c r="K3">
-        <v>-70.5</v>
+        <v>273.8</v>
       </c>
       <c r="L3">
-        <v>-0.2770137524557957</v>
+        <v>5.443339960238569</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -713,7 +740,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -722,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -733,11 +760,26 @@
       <c r="V3">
         <v>0</v>
       </c>
+      <c r="W3">
+        <v>0.3328066123738909</v>
+      </c>
       <c r="X3">
-        <v>0.1020052760592112</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="Y3">
+        <v>0.2480096839059283</v>
+      </c>
+      <c r="Z3">
+        <v>0.06114014829220858</v>
+      </c>
+      <c r="AA3">
+        <v>0.05883067947003768</v>
       </c>
       <c r="AB3">
-        <v>0.1020052760592112</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="AC3">
+        <v>-0.02596624899792487</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -767,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.983</v>
+        <v>-5.77</v>
       </c>
       <c r="AQ3">
-        <v>-255.0356052899288</v>
+        <v>-8.388214904679376</v>
       </c>
     </row>
   </sheetData>
